--- a/Attribute_Users_List.xlsx
+++ b/Attribute_Users_List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abhishek Gowda T N\OneDrive\Desktop\VibhuARMS-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8A9F27C-663E-4A18-A83F-82A9495507E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDF908E3-8C30-4EF4-81C2-3889C3775ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{2C09A346-62D9-4027-A411-FBF110D06ADC}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>name</t>
   </si>
@@ -133,6 +133,39 @@
   </si>
   <si>
     <t>password10</t>
+  </si>
+  <si>
+    <t>attributerid</t>
+  </si>
+  <si>
+    <t>ATB001</t>
+  </si>
+  <si>
+    <t>ATB002</t>
+  </si>
+  <si>
+    <t>ATB003</t>
+  </si>
+  <si>
+    <t>ATB004</t>
+  </si>
+  <si>
+    <t>ATB005</t>
+  </si>
+  <si>
+    <t>ATB006</t>
+  </si>
+  <si>
+    <t>ATB007</t>
+  </si>
+  <si>
+    <t>ATB008</t>
+  </si>
+  <si>
+    <t>ATB009</t>
+  </si>
+  <si>
+    <t>ATB010</t>
   </si>
 </sst>
 </file>
@@ -504,148 +537,181 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2625A3B-EF9A-45F8-9D7A-78A54B7E35CE}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.08984375" customWidth="1"/>
-    <col min="2" max="2" width="28.453125" customWidth="1"/>
-    <col min="3" max="3" width="18.08984375" customWidth="1"/>
+    <col min="1" max="2" width="16.08984375" customWidth="1"/>
+    <col min="3" max="3" width="28.453125" customWidth="1"/>
+    <col min="4" max="4" width="18.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>32</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{99C6916E-B909-4445-B904-FCA1B2D81933}"/>
-    <hyperlink ref="B3" r:id="rId2" xr:uid="{CCA24E83-6D86-49F5-8998-49CAF59F4361}"/>
-    <hyperlink ref="B4" r:id="rId3" xr:uid="{A387A1A3-BDC2-4F6C-885C-E4A06A3888B7}"/>
-    <hyperlink ref="B6" r:id="rId4" xr:uid="{60B8ABE9-3C71-487A-82A8-8B5108BDA7D2}"/>
-    <hyperlink ref="B8" r:id="rId5" xr:uid="{1C01A245-2793-41DF-A248-95A3631C683C}"/>
-    <hyperlink ref="B10" r:id="rId6" xr:uid="{32C7DA12-16FA-4179-8FCB-D9053671845C}"/>
-    <hyperlink ref="B5" r:id="rId7" xr:uid="{2FC8C2D9-3A02-4EE7-9084-25C8E9B6E0C4}"/>
-    <hyperlink ref="B7" r:id="rId8" xr:uid="{527374F0-8F1E-4093-A733-EFF984E57E35}"/>
-    <hyperlink ref="B9" r:id="rId9" xr:uid="{93AE8C77-D1E4-4085-8704-089C7F745E99}"/>
-    <hyperlink ref="B11" r:id="rId10" xr:uid="{C547CCF1-A25F-4335-8515-3F0A23BBC6F1}"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{99C6916E-B909-4445-B904-FCA1B2D81933}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{CCA24E83-6D86-49F5-8998-49CAF59F4361}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{A387A1A3-BDC2-4F6C-885C-E4A06A3888B7}"/>
+    <hyperlink ref="C6" r:id="rId4" xr:uid="{60B8ABE9-3C71-487A-82A8-8B5108BDA7D2}"/>
+    <hyperlink ref="C8" r:id="rId5" xr:uid="{1C01A245-2793-41DF-A248-95A3631C683C}"/>
+    <hyperlink ref="C10" r:id="rId6" xr:uid="{32C7DA12-16FA-4179-8FCB-D9053671845C}"/>
+    <hyperlink ref="C5" r:id="rId7" xr:uid="{2FC8C2D9-3A02-4EE7-9084-25C8E9B6E0C4}"/>
+    <hyperlink ref="C7" r:id="rId8" xr:uid="{527374F0-8F1E-4093-A733-EFF984E57E35}"/>
+    <hyperlink ref="C9" r:id="rId9" xr:uid="{93AE8C77-D1E4-4085-8704-089C7F745E99}"/>
+    <hyperlink ref="C11" r:id="rId10" xr:uid="{C547CCF1-A25F-4335-8515-3F0A23BBC6F1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
